--- a/data/trans_dic/IP07_C14_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 23,81</t>
+          <t>5,41; 27,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 26,38</t>
+          <t>9,74; 30,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 19,56</t>
+          <t>9,58; 25,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 49,15</t>
+          <t>17,68; 50,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 51,26</t>
+          <t>17,99; 49,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,36; 43,74</t>
+          <t>20,18; 43,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,53</t>
+          <t>0,0; 17,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 75,93</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 18,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,39</t>
+          <t>0,0; 14,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,31</t>
+          <t>0,0; 20,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,28</t>
+          <t>1,37; 12,11</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,4; 49,31</t>
+          <t>22,61; 62,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,31; 64,29</t>
+          <t>14,44; 47,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,04; 51,28</t>
+          <t>22,73; 49,68</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 43,54</t>
+          <t>15,61; 42,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,72; 43,26</t>
+          <t>13,31; 45,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 40,19</t>
+          <t>17,8; 37,89</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,48; 4,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,35</t>
+          <t>0,22; 1,98</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,09</t>
+          <t>8,94; 17,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,41</t>
+          <t>11,18; 19,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,33</t>
+          <t>10,57; 16,58</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13374</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1409; 14533</t>
+          <t>2583; 13218</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2414; 13429</t>
+          <t>3665; 11496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4780; 21896</t>
+          <t>8177; 21674</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13070</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3525; 9948</t>
+          <t>3682; 10456</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4199; 11710</t>
+          <t>3638; 10086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9201; 18844</t>
+          <t>8283; 17996</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>492</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1895</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 2231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3351</t>
+          <t>0; 3696</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>615</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1658</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3291</t>
+          <t>0; 2893</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>461; 4606</t>
+          <t>490; 4342</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12210</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2423; 8295</t>
+          <t>4116; 11305</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4773; 12625</t>
+          <t>2541; 8395</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8402; 18698</t>
+          <t>8141; 17789</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>16616</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2943; 10093</t>
+          <t>5832; 15827</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5369; 15780</t>
+          <t>3254; 11228</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10895; 23975</t>
+          <t>11001; 23417</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1083</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>378; 3480</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>337; 3313</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>374; 3383</t>
+          <t>341; 3100</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>16535; 36535</t>
+          <t>22255; 42528</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24269; 46183</t>
+          <t>21073; 36454</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45397; 73927</t>
+          <t>46261; 72535</t>
         </is>
       </c>
     </row>
